--- a/templates/gabarit_rup.xlsx
+++ b/templates/gabarit_rup.xlsx
@@ -187,421 +187,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>16</col>
-      <colOff>100853</colOff>
-      <row>0</row>
-      <rowOff>224118</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>720064</colOff>
-      <row>0</row>
-      <rowOff>643276</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="16976912" y="224118"/>
-          <a:ext cx="619211" cy="419158"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>40822</colOff>
-      <row>0</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>693964</colOff>
-      <row>0</row>
-      <rowOff>556581</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="22547036" y="95250"/>
-          <a:ext cx="653142" cy="461331"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>21</col>
-      <colOff>748393</colOff>
-      <row>0</row>
-      <rowOff>176893</rowOff>
-    </from>
-    <to>
-      <col>22</col>
-      <colOff>721178</colOff>
-      <row>0</row>
-      <rowOff>585107</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="23567572" y="176893"/>
-          <a:ext cx="734785" cy="408214"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>25</col>
-      <colOff>680357</colOff>
-      <row>0</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>26</col>
-      <colOff>747148</colOff>
-      <row>0</row>
-      <rowOff>540244</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="26996571" y="136071"/>
-          <a:ext cx="828791" cy="404173"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>81643</colOff>
-      <row>0</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>700854</colOff>
-      <row>0</row>
-      <rowOff>518463</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="27921857" y="136071"/>
-          <a:ext cx="619211" cy="382392"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>16</col>
-      <colOff>100853</colOff>
-      <row>1</row>
-      <rowOff>224118</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>720064</colOff>
-      <row>2</row>
-      <rowOff>71776</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="18188828" y="224118"/>
-          <a:ext cx="619211" cy="419158"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>20</col>
-      <colOff>40822</colOff>
-      <row>1</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>693964</colOff>
-      <row>1</row>
-      <rowOff>556581</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="22538872" y="95250"/>
-          <a:ext cx="653142" cy="461331"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>21</col>
-      <colOff>748393</colOff>
-      <row>1</row>
-      <rowOff>176893</rowOff>
-    </from>
-    <to>
-      <col>22</col>
-      <colOff>721178</colOff>
-      <row>2</row>
-      <rowOff>13607</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="24008443" y="176893"/>
-          <a:ext cx="734785" cy="408214"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>25</col>
-      <colOff>680357</colOff>
-      <row>1</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>26</col>
-      <colOff>747148</colOff>
-      <row>1</row>
-      <rowOff>540244</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="26988407" y="136071"/>
-          <a:ext cx="828791" cy="404173"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>27</col>
-      <colOff>81643</colOff>
-      <row>1</row>
-      <rowOff>136071</rowOff>
-    </from>
-    <to>
-      <col>27</col>
-      <colOff>700854</colOff>
-      <row>1</row>
-      <rowOff>518463</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="27913693" y="136071"/>
-          <a:ext cx="619211" cy="382392"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1242,6 +827,5 @@
     <row r="154"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>